--- a/Cases.xlsx
+++ b/Cases.xlsx
@@ -680,28 +680,67 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -711,45 +750,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1087,19 +1087,19 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10">
+      <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -1110,11 +1110,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
       <c r="F3" s="8" t="s">
         <v>14</v>
       </c>
@@ -1123,11 +1123,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
       <c r="F4" s="8" t="s">
         <v>15</v>
       </c>
@@ -1136,19 +1136,19 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
+      <c r="A5" s="16">
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -1159,11 +1159,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
       <c r="F6" s="8" t="s">
         <v>14</v>
       </c>
@@ -1172,11 +1172,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="8" t="s">
         <v>15</v>
       </c>
@@ -1185,19 +1185,19 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10">
+      <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="18" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -1208,11 +1208,11 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="8" t="s">
         <v>24</v>
       </c>
@@ -1221,11 +1221,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
       <c r="F10" s="8" t="s">
         <v>15</v>
       </c>
@@ -1234,19 +1234,19 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="46.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="17">
+      <c r="A11" s="11">
         <v>4</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="10" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="9" t="s">
@@ -1257,19 +1257,19 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10">
+      <c r="A12" s="16">
         <v>5</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="9" t="s">
@@ -1280,11 +1280,11 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="14"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="8" t="s">
         <v>32</v>
       </c>
@@ -1293,19 +1293,19 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10">
+      <c r="A14" s="16">
         <v>6</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F14" s="9" t="s">
@@ -1316,11 +1316,11 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="15"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="28"/>
       <c r="F15" s="8" t="s">
         <v>37</v>
       </c>
@@ -1329,19 +1329,19 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10">
+      <c r="A16" s="16">
         <v>7</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="31" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="9" t="s">
@@ -1352,11 +1352,11 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="19"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="32"/>
       <c r="F17" s="8" t="s">
         <v>43</v>
       </c>
@@ -1365,11 +1365,11 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="20"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="8" t="s">
         <v>44</v>
       </c>
@@ -1378,19 +1378,19 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="10">
+      <c r="A19" s="16">
         <v>8</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="9" t="s">
@@ -1401,11 +1401,11 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="11"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
       <c r="F20" s="8" t="s">
         <v>37</v>
       </c>
@@ -1414,11 +1414,11 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="11"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="8" t="s">
         <v>45</v>
       </c>
@@ -1427,19 +1427,19 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="10">
+      <c r="A22" s="16">
         <v>9</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="9" t="s">
@@ -1450,11 +1450,11 @@
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="11"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
       <c r="F23" s="8" t="s">
         <v>37</v>
       </c>
@@ -1463,11 +1463,11 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
       <c r="F24" s="8" t="s">
         <v>48</v>
       </c>
@@ -1476,11 +1476,11 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="11"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="9" t="s">
         <v>50</v>
       </c>
@@ -1489,19 +1489,19 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="10">
+      <c r="A26" s="16">
         <v>11</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F26" s="9" t="s">
@@ -1512,11 +1512,11 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="11"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
       <c r="F27" s="8" t="s">
         <v>37</v>
       </c>
@@ -1525,11 +1525,11 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="11"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
       <c r="F28" s="8" t="s">
         <v>48</v>
       </c>
@@ -1538,11 +1538,11 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="11"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="15"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="28"/>
       <c r="F29" s="9" t="s">
         <v>55</v>
       </c>
@@ -1551,19 +1551,19 @@
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="10">
+      <c r="A30" s="16">
         <v>12</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F30" s="9" t="s">
@@ -1574,11 +1574,11 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="11"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
       <c r="F31" s="8" t="s">
         <v>37</v>
       </c>
@@ -1587,11 +1587,11 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="11"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
       <c r="F32" s="8" t="s">
         <v>48</v>
       </c>
@@ -1600,11 +1600,11 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="11"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
       <c r="F33" s="9" t="s">
         <v>59</v>
       </c>
@@ -1613,19 +1613,19 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="10">
+      <c r="A34" s="16">
         <v>13</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F34" s="9" t="s">
@@ -1636,11 +1636,11 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="11"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
       <c r="F35" s="8" t="s">
         <v>37</v>
       </c>
@@ -1649,11 +1649,11 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="11"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
       <c r="F36" s="8" t="s">
         <v>48</v>
       </c>
@@ -1662,11 +1662,11 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="12"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
+      <c r="A37" s="27"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
       <c r="F37" s="9" t="s">
         <v>62</v>
       </c>
@@ -1675,19 +1675,19 @@
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="10">
+      <c r="A38" s="16">
         <v>14</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F38" s="9" t="s">
@@ -1698,11 +1698,11 @@
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="11"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
       <c r="F39" s="8" t="s">
         <v>37</v>
       </c>
@@ -1711,11 +1711,11 @@
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="11"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
       <c r="F40" s="8" t="s">
         <v>48</v>
       </c>
@@ -1724,11 +1724,11 @@
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="12"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
+      <c r="A41" s="27"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
       <c r="F41" s="9" t="s">
         <v>77</v>
       </c>
@@ -1737,19 +1737,19 @@
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="10">
+      <c r="A42" s="16">
         <v>15</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="18" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="9" t="s">
@@ -1760,11 +1760,11 @@
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="11"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
       <c r="F43" s="8" t="s">
         <v>37</v>
       </c>
@@ -1773,11 +1773,11 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="11"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
       <c r="F44" s="8" t="s">
         <v>48</v>
       </c>
@@ -1786,11 +1786,11 @@
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="12"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="15"/>
+      <c r="A45" s="27"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="28"/>
       <c r="F45" s="9" t="s">
         <v>65</v>
       </c>
@@ -1799,19 +1799,19 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="10">
+      <c r="A46" s="16">
         <v>16</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D46" s="28" t="s">
+      <c r="D46" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="22" t="s">
+      <c r="E46" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F46" s="9" t="s">
@@ -1822,11 +1822,11 @@
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="11"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="26"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="25"/>
       <c r="F47" s="8" t="s">
         <v>37</v>
       </c>
@@ -1835,11 +1835,11 @@
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="11"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="26"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="25"/>
       <c r="F48" s="8" t="s">
         <v>70</v>
       </c>
@@ -1848,11 +1848,11 @@
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="12"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="27"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="30"/>
       <c r="F49" s="9" t="s">
         <v>72</v>
       </c>
@@ -1861,19 +1861,19 @@
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="10">
+      <c r="A50" s="16">
         <v>17</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="D50" s="28" t="s">
+      <c r="D50" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="22" t="s">
+      <c r="E50" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F50" s="9" t="s">
@@ -1884,11 +1884,11 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="11"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="26"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="25"/>
       <c r="F51" s="8" t="s">
         <v>37</v>
       </c>
@@ -1897,11 +1897,11 @@
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="11"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="26"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="25"/>
       <c r="F52" s="8" t="s">
         <v>70</v>
       </c>
@@ -1910,11 +1910,11 @@
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="12"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="27"/>
+      <c r="A53" s="27"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="30"/>
       <c r="F53" s="9" t="s">
         <v>80</v>
       </c>
@@ -1923,19 +1923,19 @@
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="10">
+      <c r="A54" s="16">
         <v>18</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D54" s="28" t="s">
+      <c r="D54" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="22" t="s">
+      <c r="E54" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F54" s="9" t="s">
@@ -1946,11 +1946,11 @@
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="11"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="26"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="25"/>
       <c r="F55" s="8" t="s">
         <v>37</v>
       </c>
@@ -1959,11 +1959,11 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="11"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="26"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="25"/>
       <c r="F56" s="8" t="s">
         <v>70</v>
       </c>
@@ -1972,11 +1972,11 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="12"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="27"/>
+      <c r="A57" s="27"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="30"/>
       <c r="F57" s="9" t="s">
         <v>85</v>
       </c>
@@ -1985,19 +1985,19 @@
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="10">
+      <c r="A58" s="16">
         <v>19</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D58" s="28" t="s">
+      <c r="D58" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E58" s="22" t="s">
+      <c r="E58" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F58" s="9" t="s">
@@ -2008,11 +2008,11 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="11"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="26"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="25"/>
       <c r="F59" s="8" t="s">
         <v>37</v>
       </c>
@@ -2021,11 +2021,11 @@
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="11"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="26"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="25"/>
       <c r="F60" s="8" t="s">
         <v>70</v>
       </c>
@@ -2034,11 +2034,11 @@
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="12"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="27"/>
+      <c r="A61" s="27"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="30"/>
       <c r="F61" s="9" t="s">
         <v>104</v>
       </c>
@@ -2047,19 +2047,19 @@
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="10">
+      <c r="A62" s="16">
         <v>20</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D62" s="28" t="s">
+      <c r="D62" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="22" t="s">
+      <c r="E62" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F62" s="9" t="s">
@@ -2070,11 +2070,11 @@
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="11"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="26"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="25"/>
       <c r="F63" s="8" t="s">
         <v>37</v>
       </c>
@@ -2083,11 +2083,11 @@
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="11"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="26"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="25"/>
       <c r="F64" s="8" t="s">
         <v>91</v>
       </c>
@@ -2096,11 +2096,11 @@
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="12"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="28"/>
-      <c r="E65" s="27"/>
+      <c r="A65" s="27"/>
+      <c r="B65" s="28"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="30"/>
       <c r="F65" s="9" t="s">
         <v>93</v>
       </c>
@@ -2109,19 +2109,19 @@
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="10">
+      <c r="A66" s="16">
         <v>21</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D66" s="28" t="s">
+      <c r="D66" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F66" s="9" t="s">
@@ -2132,11 +2132,11 @@
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="11"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="26"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="25"/>
       <c r="F67" s="8" t="s">
         <v>37</v>
       </c>
@@ -2145,11 +2145,11 @@
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="11"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="24"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="26"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="25"/>
       <c r="F68" s="8" t="s">
         <v>96</v>
       </c>
@@ -2158,11 +2158,11 @@
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="12"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="27"/>
+      <c r="A69" s="27"/>
+      <c r="B69" s="28"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="30"/>
       <c r="F69" s="9" t="s">
         <v>97</v>
       </c>
@@ -2171,19 +2171,19 @@
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="10">
+      <c r="A70" s="16">
         <v>21</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="D70" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="22" t="s">
+      <c r="E70" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F70" s="9" t="s">
@@ -2194,11 +2194,11 @@
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="11"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="28"/>
-      <c r="E71" s="26"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="25"/>
       <c r="F71" s="8" t="s">
         <v>37</v>
       </c>
@@ -2207,11 +2207,11 @@
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="11"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="24"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="26"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="25"/>
       <c r="F72" s="8" t="s">
         <v>96</v>
       </c>
@@ -2220,11 +2220,11 @@
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="12"/>
-      <c r="B73" s="15"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="28"/>
-      <c r="E73" s="27"/>
+      <c r="A73" s="27"/>
+      <c r="B73" s="28"/>
+      <c r="C73" s="29"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="30"/>
       <c r="F73" s="9" t="s">
         <v>85</v>
       </c>
@@ -2233,19 +2233,19 @@
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="10">
+      <c r="A74" s="16">
         <v>21</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D74" s="28" t="s">
+      <c r="D74" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E74" s="22" t="s">
+      <c r="E74" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F74" s="9" t="s">
@@ -2256,11 +2256,11 @@
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="11"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="26"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="25"/>
       <c r="F75" s="8" t="s">
         <v>37</v>
       </c>
@@ -2269,11 +2269,11 @@
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="11"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="28"/>
-      <c r="E76" s="26"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="25"/>
       <c r="F76" s="8" t="s">
         <v>96</v>
       </c>
@@ -2282,11 +2282,11 @@
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="12"/>
-      <c r="B77" s="15"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="28"/>
-      <c r="E77" s="27"/>
+      <c r="A77" s="27"/>
+      <c r="B77" s="28"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="30"/>
       <c r="F77" s="9" t="s">
         <v>104</v>
       </c>
@@ -2295,19 +2295,19 @@
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="10">
+      <c r="A78" s="16">
         <v>22</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="D78" s="28" t="s">
+      <c r="D78" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E78" s="22" t="s">
+      <c r="E78" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F78" s="9" t="s">
@@ -2318,11 +2318,11 @@
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="11"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="24"/>
-      <c r="D79" s="28"/>
-      <c r="E79" s="26"/>
+      <c r="A79" s="17"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="25"/>
       <c r="F79" s="8" t="s">
         <v>37</v>
       </c>
@@ -2331,11 +2331,11 @@
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="11"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="28"/>
-      <c r="E80" s="26"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="22"/>
+      <c r="E80" s="25"/>
       <c r="F80" s="8" t="s">
         <v>96</v>
       </c>
@@ -2344,11 +2344,11 @@
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="12"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="28"/>
-      <c r="E81" s="27"/>
+      <c r="A81" s="27"/>
+      <c r="B81" s="28"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="30"/>
       <c r="F81" s="9" t="s">
         <v>80</v>
       </c>
@@ -2357,19 +2357,19 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="10">
+      <c r="A82" s="16">
         <v>23</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C82" s="23" t="s">
+      <c r="C82" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="D82" s="28" t="s">
+      <c r="D82" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E82" s="22" t="s">
+      <c r="E82" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F82" s="9" t="s">
@@ -2380,11 +2380,11 @@
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="11"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="24"/>
-      <c r="D83" s="28"/>
-      <c r="E83" s="26"/>
+      <c r="A83" s="17"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="25"/>
       <c r="F83" s="8" t="s">
         <v>111</v>
       </c>
@@ -2393,11 +2393,11 @@
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="11"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="24"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="26"/>
+      <c r="A84" s="17"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="25"/>
       <c r="F84" s="8" t="s">
         <v>112</v>
       </c>
@@ -2406,19 +2406,19 @@
       </c>
     </row>
     <row r="85" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="17">
-        <v>23</v>
-      </c>
-      <c r="B85" s="16" t="s">
+      <c r="A85" s="11">
+        <v>24</v>
+      </c>
+      <c r="B85" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C85" s="29" t="s">
+      <c r="C85" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D85" s="30" t="s">
+      <c r="D85" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="21" t="s">
+      <c r="E85" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F85" s="9" t="s">
@@ -2429,19 +2429,19 @@
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="10">
-        <v>23</v>
-      </c>
-      <c r="B86" s="13" t="s">
+      <c r="A86" s="16">
+        <v>25</v>
+      </c>
+      <c r="B86" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D86" s="28" t="s">
+      <c r="D86" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E86" s="22" t="s">
+      <c r="E86" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F86" s="9" t="s">
@@ -2452,11 +2452,11 @@
       </c>
     </row>
     <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="11"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="24"/>
-      <c r="D87" s="28"/>
-      <c r="E87" s="26"/>
+      <c r="A87" s="17"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="22"/>
+      <c r="E87" s="25"/>
       <c r="F87" s="8" t="s">
         <v>122</v>
       </c>
@@ -2465,11 +2465,11 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="11"/>
-      <c r="B88" s="14"/>
-      <c r="C88" s="24"/>
-      <c r="D88" s="31"/>
-      <c r="E88" s="26"/>
+      <c r="A88" s="17"/>
+      <c r="B88" s="19"/>
+      <c r="C88" s="21"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="25"/>
       <c r="F88" s="7" t="s">
         <v>112</v>
       </c>
@@ -2478,53 +2478,143 @@
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="32">
-        <v>23</v>
-      </c>
-      <c r="B89" s="28" t="s">
+      <c r="A89" s="26">
+        <v>26</v>
+      </c>
+      <c r="B89" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="C89" s="28" t="s">
+      <c r="C89" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="D89" s="28" t="s">
+      <c r="D89" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="28" t="s">
+      <c r="E89" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F89" s="33" t="s">
+      <c r="F89" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="G89" s="33" t="s">
+      <c r="G89" s="15" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="32"/>
-      <c r="B90" s="28"/>
-      <c r="C90" s="28"/>
-      <c r="D90" s="28"/>
-      <c r="E90" s="28"/>
-      <c r="F90" s="33" t="s">
+      <c r="A90" s="26"/>
+      <c r="B90" s="22"/>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="G90" s="33" t="s">
+      <c r="G90" s="15" t="s">
         <v>118</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="125">
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="D86:D88"/>
-    <mergeCell ref="E86:E88"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="D89:D90"/>
-    <mergeCell ref="E89:E90"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="C38:C41"/>
+    <mergeCell ref="D38:D41"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="D58:D61"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="E70:E73"/>
     <mergeCell ref="A82:A84"/>
     <mergeCell ref="B82:B84"/>
     <mergeCell ref="C82:C84"/>
@@ -2540,106 +2630,16 @@
     <mergeCell ref="C78:C81"/>
     <mergeCell ref="D78:D81"/>
     <mergeCell ref="E78:E81"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="E66:E69"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="D58:D61"/>
-    <mergeCell ref="E58:E61"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="E62:E65"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="C38:C41"/>
-    <mergeCell ref="D38:D41"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="E30:E33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="E26:E29"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="C86:C88"/>
+    <mergeCell ref="D86:D88"/>
+    <mergeCell ref="E86:E88"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="D89:D90"/>
+    <mergeCell ref="E89:E90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
